--- a/exports/HAL_full_report.xlsx
+++ b/exports/HAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>680.1</v>
+        <v>667</v>
       </c>
       <c r="I2" t="n">
         <v>672.2135260806169</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.84</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.26</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>675.5</v>
+        <v>690.2</v>
       </c>
       <c r="I3" t="n">
         <v>682.3784431415846</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.27</v>
+        <v>-3.48</v>
       </c>
       <c r="L3" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.2</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.27</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44678.55208333334</v>
+        <v>44679.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>818.5</v>
+        <v>812.1</v>
       </c>
       <c r="I4" t="n">
         <v>812.4123273144864</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>58</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>18.59</v>
+        <v>17.66</v>
       </c>
       <c r="L4" t="n">
         <v>5.46</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>804.4</v>
+        <v>827.65</v>
       </c>
       <c r="I5" t="n">
         <v>823.225603237034</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>0.95</v>
+        <v>-1.91</v>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="M5" t="n">
         <v>2.07</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44729.55208333334</v>
+        <v>44732.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>966.5</v>
+        <v>876.05</v>
       </c>
       <c r="I6" t="n">
         <v>895.6802748489943</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>16.78</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>2.61</v>
@@ -783,7 +854,7 @@
         <v>2.38</v>
       </c>
       <c r="N6" t="n">
-        <v>3.36</v>
+        <v>10.82</v>
       </c>
       <c r="O6" t="n">
         <v>4.18</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>16.55</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44760.55208333334</v>
+        <v>44761.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>889.5</v>
+        <v>904.9</v>
       </c>
       <c r="I7" t="n">
         <v>898.7797016822304</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.54</v>
+        <v>-3.29</v>
       </c>
       <c r="L7" t="n">
         <v>10.67</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.44</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1240</v>
+        <v>1222.45</v>
       </c>
       <c r="I8" t="n">
         <v>1228.670989584511</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K8" t="n">
-        <v>37.03</v>
+        <v>35.09</v>
       </c>
       <c r="L8" t="n">
         <v>1.92</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44840.38541666666</v>
+        <v>44840.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>1234.5</v>
+        <v>1238</v>
       </c>
       <c r="I9" t="n">
         <v>1235.533991628133</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.99</v>
+        <v>-1.27</v>
       </c>
       <c r="L9" t="n">
         <v>3.48</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.55</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1249.5</v>
+        <v>1226.7</v>
       </c>
       <c r="I10" t="n">
         <v>1231.526428310786</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>0.93</v>
+        <v>-0.91</v>
       </c>
       <c r="L10" t="n">
         <v>5.86</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.25</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44880.55208333334</v>
+        <v>44881.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1261.55</v>
+        <v>1338.35</v>
       </c>
       <c r="I11" t="n">
         <v>1290.428360385293</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.84</v>
+        <v>-9.1</v>
       </c>
       <c r="L11" t="n">
-        <v>3.24</v>
+        <v>9.85</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>6.06</v>
       </c>
       <c r="O11" t="n">
         <v>-2.46</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.51</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44909.55208333334</v>
+        <v>44910.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1341.25</v>
+        <v>1314.45</v>
       </c>
       <c r="I12" t="n">
         <v>1337.307859106541</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>0.22</v>
+        <v>-1.79</v>
       </c>
       <c r="L12" t="n">
         <v>5.71</v>
@@ -1125,7 +1268,7 @@
         <v>0.54</v>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>3.06</v>
       </c>
       <c r="O12" t="n">
         <v>6.06</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.01</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44949.55208333334</v>
+        <v>44950.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1261.6</v>
+        <v>1269.8</v>
       </c>
       <c r="I13" t="n">
         <v>1263.231719660425</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>4.02</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
         <v>2.31</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>4.21</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44958.38541666666</v>
+        <v>44958.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1232.7</v>
+        <v>1180.1</v>
       </c>
       <c r="I14" t="n">
         <v>1224.39046035475</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.92</v>
+        <v>-7.06</v>
       </c>
       <c r="L14" t="n">
-        <v>4.78</v>
+        <v>9.43</v>
       </c>
       <c r="M14" t="n">
         <v>0.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>9.42</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1241</v>
+        <v>1290.5</v>
       </c>
       <c r="I15" t="n">
         <v>1270.111541959676</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.16</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>5.71</v>
+        <v>9.74</v>
       </c>
       <c r="M15" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>7.29</v>
       </c>
       <c r="O15" t="n">
         <v>-4.52</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45002.55208333334</v>
+        <v>45005.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1403</v>
+        <v>1320.5</v>
       </c>
       <c r="I16" t="n">
         <v>1348.886376658428</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K16" t="n">
-        <v>8.720000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="L16" t="n">
         <v>3.72</v>
       </c>
       <c r="M16" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.56</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
         <v>7.29</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1317.25</v>
+        <v>1353.5</v>
       </c>
       <c r="I17" t="n">
         <v>1351.539237808398</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>-2.5</v>
       </c>
       <c r="L17" t="n">
         <v>5.56</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.78</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1885.9</v>
+        <v>1831.5</v>
       </c>
       <c r="I18" t="n">
         <v>1841.828087989791</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>85</v>
+        <v>85.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>39.34</v>
+        <v>35.32</v>
       </c>
       <c r="L18" t="n">
         <v>2.73</v>
@@ -1467,7 +1682,7 @@
         <v>1.44</v>
       </c>
       <c r="N18" t="n">
-        <v>1.77</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>3.05</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>9.41</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45117.55208333334</v>
+        <v>45118.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1891.5</v>
+        <v>1966.6</v>
       </c>
       <c r="I19" t="n">
         <v>1950.824936822428</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.28</v>
+        <v>-7.38</v>
       </c>
       <c r="L19" t="n">
-        <v>5.38</v>
+        <v>7.7</v>
       </c>
       <c r="M19" t="n">
         <v>0.72</v>
       </c>
       <c r="N19" t="n">
-        <v>1.98</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
         <v>-3.55</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1935.5</v>
+        <v>1884</v>
       </c>
       <c r="I20" t="n">
         <v>1910.682691644497</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.58</v>
+        <v>-4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>4.02</v>
+        <v>4.66</v>
       </c>
       <c r="M20" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.24</v>
+        <v>3.33</v>
       </c>
       <c r="O20" t="n">
         <v>3.7</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.7</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1946.5</v>
+        <v>2007.7</v>
       </c>
       <c r="I21" t="n">
         <v>1955.129711219323</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.32</v>
+        <v>-6.57</v>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>6.82</v>
       </c>
       <c r="M21" t="n">
         <v>0.37</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>3.79</v>
       </c>
       <c r="O21" t="n">
         <v>-3.33</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.04</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1982.4</v>
+        <v>1975</v>
       </c>
       <c r="I22" t="n">
         <v>1978.693840539133</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.26</v>
+        <v>-1.63</v>
       </c>
       <c r="L22" t="n">
         <v>3.49</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.78</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1855.7</v>
+        <v>1895.7</v>
       </c>
       <c r="I23" t="n">
         <v>1886.807180427914</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>6.04</v>
+        <v>4.02</v>
       </c>
       <c r="L23" t="n">
         <v>4.08</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>2925</v>
+        <v>2895.75</v>
       </c>
       <c r="I24" t="n">
         <v>2902.035435351268</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>81</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>54.3</v>
+        <v>52.75</v>
       </c>
       <c r="L24" t="n">
         <v>2.04</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45329.55208333334</v>
+        <v>45330.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2948</v>
+        <v>3121.95</v>
       </c>
       <c r="I25" t="n">
         <v>3060.665877997231</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.8</v>
+        <v>-7.81</v>
       </c>
       <c r="L25" t="n">
-        <v>6.16</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
         <v>0.67</v>
       </c>
       <c r="N25" t="n">
-        <v>2.72</v>
+        <v>5.6</v>
       </c>
       <c r="O25" t="n">
         <v>-3.54</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2971</v>
+        <v>2888.4</v>
       </c>
       <c r="I26" t="n">
         <v>2919.550640147201</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.84</v>
+        <v>-7.48</v>
       </c>
       <c r="L26" t="n">
-        <v>6.47</v>
+        <v>7.63</v>
       </c>
       <c r="M26" t="n">
         <v>-0</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.43</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45348.55208333334</v>
+        <v>45349.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3054</v>
+        <v>3114.5</v>
       </c>
       <c r="I27" t="n">
         <v>3091.543429999421</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.73</v>
+        <v>-7.83</v>
       </c>
       <c r="L27" t="n">
-        <v>7.81</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>6.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3274.9</v>
+        <v>3075.85</v>
       </c>
       <c r="I28" t="n">
         <v>3188.642505398977</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>5.15</v>
+        <v>-1.24</v>
       </c>
       <c r="L28" t="n">
         <v>3.22</v>
       </c>
       <c r="M28" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>7.39</v>
       </c>
       <c r="O28" t="n">
         <v>1.28</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.72</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45373.55208333334</v>
+        <v>45377.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3169</v>
+        <v>3272.65</v>
       </c>
       <c r="I29" t="n">
         <v>3249.902363500665</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.03</v>
+        <v>-6.4</v>
       </c>
       <c r="L29" t="n">
-        <v>6.32</v>
+        <v>6.7</v>
       </c>
       <c r="M29" t="n">
         <v>1.23</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.92</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45418.38541666666</v>
+        <v>45418.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>3839.75</v>
+        <v>3822</v>
       </c>
       <c r="I30" t="n">
         <v>3828.919910090957</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>17.33</v>
+        <v>16.79</v>
       </c>
       <c r="L30" t="n">
         <v>2.83</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>5.27</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45425.55208333334</v>
+        <v>45426.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3933.8</v>
+        <v>4036</v>
       </c>
       <c r="I31" t="n">
         <v>3941.805107836293</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.93</v>
+        <v>-5.6</v>
       </c>
       <c r="L31" t="n">
-        <v>3.45</v>
+        <v>6.41</v>
       </c>
       <c r="M31" t="n">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
       <c r="N31" t="n">
         <v>3.99</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>6.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>5287.45</v>
+        <v>4561.6</v>
       </c>
       <c r="I32" t="n">
         <v>4813.197740669092</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>31.01</v>
+        <v>13.02</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>0.24</v>
+        <v>2.69</v>
       </c>
       <c r="N32" t="n">
-        <v>2.47</v>
+        <v>17.26</v>
       </c>
       <c r="O32" t="n">
         <v>3.69</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>17.63</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45456.38541666666</v>
+        <v>45456.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>4913.1</v>
+        <v>5115</v>
       </c>
       <c r="I33" t="n">
         <v>5114.655447052232</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.71</v>
+        <v>-12.13</v>
       </c>
       <c r="L33" t="n">
         <v>12.79</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.86</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45489.38541666666</v>
+        <v>45489.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>5410.9</v>
+        <v>5323</v>
       </c>
       <c r="I34" t="n">
         <v>5338.510084645523</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K34" t="n">
-        <v>5.78</v>
+        <v>4.07</v>
       </c>
       <c r="L34" t="n">
         <v>4.11</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>6.02</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45537.55208333334</v>
+        <v>45538.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>4685.75</v>
+        <v>4839.95</v>
       </c>
       <c r="I35" t="n">
         <v>4782.490757315881</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>11.97</v>
+        <v>9.07</v>
       </c>
       <c r="L35" t="n">
         <v>1.71</v>
       </c>
       <c r="M35" t="n">
-        <v>2.38</v>
+        <v>5.06</v>
       </c>
       <c r="N35" t="n">
         <v>4.89</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>4.45</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>4703</v>
+        <v>4591.85</v>
       </c>
       <c r="I36" t="n">
         <v>4624.381103462546</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.83</v>
+        <v>-5.13</v>
       </c>
       <c r="L36" t="n">
-        <v>2.99</v>
+        <v>5.35</v>
       </c>
       <c r="M36" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="N36" t="n">
         <v>1.78</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>4391.6</v>
+        <v>4476.4</v>
       </c>
       <c r="I37" t="n">
         <v>4406.051432114263</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K37" t="n">
-        <v>4.36</v>
+        <v>2.51</v>
       </c>
       <c r="L37" t="n">
         <v>3.16</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.93</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>4496.95</v>
+        <v>4325</v>
       </c>
       <c r="I38" t="n">
         <v>4443.153157496517</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K38" t="n">
-        <v>0.46</v>
+        <v>-3.38</v>
       </c>
       <c r="L38" t="n">
-        <v>2.49</v>
+        <v>3.61</v>
       </c>
       <c r="M38" t="n">
         <v>0.43</v>
       </c>
       <c r="N38" t="n">
-        <v>3.03</v>
+        <v>4.25</v>
       </c>
       <c r="O38" t="n">
         <v>2.06</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.07</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45602.55208333334</v>
+        <v>45603.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>4390</v>
+        <v>4443.5</v>
       </c>
       <c r="I39" t="n">
         <v>4397.298293728563</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.5</v>
+        <v>-2.74</v>
       </c>
       <c r="L39" t="n">
         <v>4.23</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>6.05</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4230</v>
+        <v>4091.2</v>
       </c>
       <c r="I40" t="n">
         <v>4213.468020286221</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.8</v>
+        <v>-7.93</v>
       </c>
       <c r="L40" t="n">
-        <v>5.01</v>
+        <v>8.4</v>
       </c>
       <c r="M40" t="n">
-        <v>-0</v>
+        <v>0.24</v>
       </c>
       <c r="N40" t="n">
         <v>4.67</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.23</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>4289.95</v>
+        <v>4376.25</v>
       </c>
       <c r="I41" t="n">
         <v>4295.763019503726</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.86</v>
+        <v>-6.97</v>
       </c>
       <c r="L41" t="n">
-        <v>5.57</v>
+        <v>7.75</v>
       </c>
       <c r="M41" t="n">
         <v>4.16</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.6</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>4612.95</v>
+        <v>4507</v>
       </c>
       <c r="I42" t="n">
         <v>4535.582746371161</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K42" t="n">
-        <v>5.41</v>
+        <v>2.99</v>
       </c>
       <c r="L42" t="n">
         <v>1.72</v>
@@ -2835,7 +3338,7 @@
         <v>0.05</v>
       </c>
       <c r="N42" t="n">
-        <v>1.33</v>
+        <v>2.79</v>
       </c>
       <c r="O42" t="n">
         <v>1.75</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.21</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>3925.95</v>
+        <v>4105.45</v>
       </c>
       <c r="I43" t="n">
         <v>4033.484377064324</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K43" t="n">
-        <v>12.89</v>
+        <v>8.91</v>
       </c>
       <c r="L43" t="n">
         <v>2.68</v>
@@ -2892,7 +3407,7 @@
         <v>1.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.48</v>
+        <v>4.94</v>
       </c>
       <c r="O43" t="n">
         <v>-2.79</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>4054</v>
+        <v>3864.3</v>
       </c>
       <c r="I44" t="n">
         <v>3950.297178543558</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.25</v>
+        <v>-5.87</v>
       </c>
       <c r="L44" t="n">
-        <v>5.44</v>
+        <v>6.8</v>
       </c>
       <c r="M44" t="n">
         <v>0.04</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="O44" t="n">
         <v>4.94</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.68</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>3792.05</v>
+        <v>3931</v>
       </c>
       <c r="I45" t="n">
         <v>3927.429385698953</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>1.87</v>
+        <v>-1.73</v>
       </c>
       <c r="L45" t="n">
         <v>5.53</v>
@@ -3006,7 +3545,7 @@
         <v>0.59</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>4.51</v>
       </c>
       <c r="O45" t="n">
         <v>-3.72</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>3772</v>
+        <v>3540.6</v>
       </c>
       <c r="I46" t="n">
         <v>3638.701247523786</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.04</v>
+        <v>-9.93</v>
       </c>
       <c r="L46" t="n">
-        <v>6.34</v>
+        <v>10.58</v>
       </c>
       <c r="M46" t="n">
-        <v>-0</v>
+        <v>1.38</v>
       </c>
       <c r="N46" t="n">
-        <v>4.82</v>
+        <v>6.28</v>
       </c>
       <c r="O46" t="n">
         <v>4.51</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.48</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>3310</v>
+        <v>3404.25</v>
       </c>
       <c r="I47" t="n">
         <v>3342.989922030899</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>6.51</v>
+        <v>3.85</v>
       </c>
       <c r="L47" t="n">
         <v>8.85</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>4238</v>
+        <v>3951.35</v>
       </c>
       <c r="I48" t="n">
         <v>4001.641127238867</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K48" t="n">
-        <v>24.49</v>
+        <v>16.07</v>
       </c>
       <c r="L48" t="n">
         <v>3.18</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7</v>
+        <v>9.84</v>
       </c>
       <c r="N48" t="n">
-        <v>3.31</v>
+        <v>4.81</v>
       </c>
       <c r="O48" t="n">
         <v>3.56</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45772.55208333334</v>
+        <v>45775.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>4183</v>
+        <v>4423.4</v>
       </c>
       <c r="I49" t="n">
         <v>4338.263844274049</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.86</v>
+        <v>-11.95</v>
       </c>
       <c r="L49" t="n">
-        <v>10.46</v>
+        <v>12.36</v>
       </c>
       <c r="M49" t="n">
         <v>3.63</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>5.81</v>
       </c>
       <c r="O49" t="n">
         <v>-4.81</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>4992.9</v>
+        <v>4863.4</v>
       </c>
       <c r="I50" t="n">
         <v>4895.764969719946</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K50" t="n">
-        <v>12.87</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L50" t="n">
         <v>5.04</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.67</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45842.55208333334</v>
+        <v>45845.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>4985.7</v>
+        <v>5031.3</v>
       </c>
       <c r="I51" t="n">
         <v>5023.812877310514</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.51</v>
+        <v>-3.45</v>
       </c>
       <c r="L51" t="n">
         <v>4.04</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>4.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>4859.9</v>
+        <v>4815.8</v>
       </c>
       <c r="I52" t="n">
         <v>4853.840263552991</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.41</v>
+        <v>-4.28</v>
       </c>
       <c r="L52" t="n">
-        <v>4.21</v>
+        <v>4.6</v>
       </c>
       <c r="M52" t="n">
         <v>0.63</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.05</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>4454</v>
+        <v>4543.9</v>
       </c>
       <c r="I53" t="n">
         <v>4537.629773455368</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K53" t="n">
-        <v>7.51</v>
+        <v>5.65</v>
       </c>
       <c r="L53" t="n">
         <v>1.52</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.81</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>4752</v>
+        <v>4715</v>
       </c>
       <c r="I54" t="n">
         <v>4750.573035062398</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>4.58</v>
+        <v>3.77</v>
       </c>
       <c r="L54" t="n">
         <v>2.5</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>4.14</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>4860</v>
+        <v>4916.9</v>
       </c>
       <c r="I55" t="n">
         <v>4910.248498073404</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.08</v>
+        <v>-4.28</v>
       </c>
       <c r="L55" t="n">
-        <v>3.99</v>
+        <v>5.58</v>
       </c>
       <c r="M55" t="n">
         <v>0.77</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>4.04</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>4727.9</v>
+        <v>4712.9</v>
       </c>
       <c r="I56" t="n">
         <v>4718.135355760042</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.84</v>
+        <v>-4.15</v>
       </c>
       <c r="L56" t="n">
-        <v>4.28</v>
+        <v>4.72</v>
       </c>
       <c r="M56" t="n">
         <v>0.02</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.36</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45968.55208333334</v>
+        <v>45971.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>4625</v>
+        <v>4780</v>
       </c>
       <c r="I57" t="n">
         <v>4715.157815530124</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
-        <v>1.87</v>
+        <v>-1.42</v>
       </c>
       <c r="L57" t="n">
-        <v>0.68</v>
+        <v>1.57</v>
       </c>
       <c r="M57" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>0.84</v>
+        <v>3.57</v>
       </c>
       <c r="O57" t="n">
         <v>-0.59</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.32</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>4729</v>
+        <v>4621.1</v>
       </c>
       <c r="I58" t="n">
         <v>4696.684231856855</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.07</v>
+        <v>-3.32</v>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="M58" t="n">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="N58" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="O58" t="n">
         <v>3.57</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.99</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>4383</v>
+        <v>4421.2</v>
       </c>
       <c r="I59" t="n">
         <v>4394.597577634649</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K59" t="n">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="L59" t="n">
         <v>1.88</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>3.94</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46042.38541666666</v>
+        <v>46042.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>4402.4</v>
+        <v>4350</v>
       </c>
       <c r="I60" t="n">
         <v>4373.598207006792</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.43</v>
+        <v>-1.61</v>
       </c>
       <c r="L60" t="n">
         <v>2.63</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.4</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>4367.7</v>
+        <v>4514</v>
       </c>
       <c r="I61" t="n">
         <v>4496.20172992434</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.41</v>
+        <v>-3.77</v>
       </c>
       <c r="L61" t="n">
-        <v>1.32</v>
+        <v>4.18</v>
       </c>
       <c r="M61" t="n">
         <v>0.93</v>
       </c>
       <c r="N61" t="n">
-        <v>2.49</v>
+        <v>6.07</v>
       </c>
       <c r="O61" t="n">
         <v>-3.38</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.96</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>4370</v>
+        <v>4254.7</v>
       </c>
       <c r="I62" t="n">
         <v>4348.009496985776</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.19</v>
+        <v>-5.74</v>
       </c>
       <c r="L62" t="n">
         <v>7.73</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>12.05</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>3680.5</v>
+        <v>3741.3</v>
       </c>
       <c r="I63" t="n">
         <v>3724.686262719095</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K63" t="n">
-        <v>13.5</v>
+        <v>12.07</v>
       </c>
       <c r="L63" t="n">
         <v>8.31</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>4605</v>
+        <v>4427.2</v>
       </c>
       <c r="I64" t="n">
         <v>4555.399437378008</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K64" t="n">
-        <v>23.09</v>
+        <v>18.33</v>
       </c>
       <c r="L64" t="n">
         <v>2.15</v>
@@ -4089,7 +4856,7 @@
         <v>1.64</v>
       </c>
       <c r="N64" t="n">
-        <v>3.73</v>
+        <v>4.95</v>
       </c>
       <c r="O64" t="n">
         <v>1.78</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.73</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>4260</v>
+        <v>4383.9</v>
       </c>
       <c r="I65" t="n">
         <v>4376.093201572555</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K65" t="n">
-        <v>3.78</v>
+        <v>0.98</v>
       </c>
       <c r="L65" t="n">
         <v>4.31</v>
@@ -4146,7 +4925,7 @@
         <v>1.17</v>
       </c>
       <c r="N65" t="n">
-        <v>2.34</v>
+        <v>5.26</v>
       </c>
       <c r="O65" t="n">
         <v>-4.95</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.87</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46258.55208333334</v>
+        <v>46259.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>4875</v>
+        <v>4863.9</v>
       </c>
       <c r="I66" t="n">
         <v>4867.002697384705</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>68.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K66" t="n">
-        <v>11.2</v>
+        <v>10.95</v>
       </c>
       <c r="L66" t="n">
         <v>2.6</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.15</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46268.55208333334</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>4770</v>
+        <v>4921.9</v>
       </c>
       <c r="I67" t="n">
         <v>4914.706573875281</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K67" t="n">
-        <v>1.93</v>
+        <v>-1.19</v>
       </c>
       <c r="L67" t="n">
         <v>1.52</v>
       </c>
       <c r="M67" t="n">
-        <v>0.35</v>
+        <v>1.28</v>
       </c>
       <c r="N67" t="n">
-        <v>0.29</v>
+        <v>2.39</v>
       </c>
       <c r="O67" t="n">
         <v>0.29</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.9</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>4917</v>
+        <v>4746.9</v>
       </c>
       <c r="I68" t="n">
         <v>4829.083375875412</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.1</v>
+        <v>-3.56</v>
       </c>
       <c r="L68" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
         <v>0.16</v>
       </c>
       <c r="N68" t="n">
-        <v>1.84</v>
+        <v>4.74</v>
       </c>
       <c r="O68" t="n">
         <v>2.39</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>4670.3</v>
+        <v>4806</v>
       </c>
       <c r="I69" t="n">
         <v>4791.839343149943</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K69" t="n">
-        <v>1.61</v>
+        <v>-1.25</v>
       </c>
       <c r="L69" t="n">
         <v>4.07</v>
@@ -4374,7 +5201,7 @@
         <v>0.58</v>
       </c>
       <c r="N69" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="O69" t="n">
         <v>-4.74</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.82</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>4874.4</v>
+        <v>4740.7</v>
       </c>
       <c r="I70" t="n">
         <v>4791.12041563167</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K70" t="n">
-        <v>1.42</v>
+        <v>-1.36</v>
       </c>
       <c r="L70" t="n">
         <v>4.49</v>
@@ -4431,7 +5270,7 @@
         <v>1.2</v>
       </c>
       <c r="N70" t="n">
-        <v>2.49</v>
+        <v>2.98</v>
       </c>
       <c r="O70" t="n">
         <v>3.4</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>6</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.58</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.27</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.78</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.3</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.6</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.02</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="21">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7650,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.16</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.23</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.48</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
